--- a/src/main/resources/rules/rules_dynamic_test.xlsx
+++ b/src/main/resources/rules/rules_dynamic_test.xlsx
@@ -5,13 +5,13 @@
     <workbookView xWindow="0" yWindow="40" windowWidth="15960" windowHeight="18080"/>
   </bookViews>
   <sheets>
-    <sheet name="Trading Conditions Test" sheetId="1" r:id="rId4"/>
+    <sheet name="Trading Conditions" sheetId="1" r:id="rId4"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="136">
   <si>
     <t>RuleSet</t>
   </si>
@@ -79,6 +79,75 @@
     <t>getString("/account/noOFSActivityLast24Months") == "$1"</t>
   </si>
   <si>
+    <t>getString("/account/noBuybackActivityLast24Months") == "$1"</t>
+  </si>
+  <si>
+    <t>getString("/account/noOpenOfferActivityLast24Months") == "$1"</t>
+  </si>
+  <si>
+    <t>getString("/account/noIPOSubscriptionLast24Months") == "$1"</t>
+  </si>
+  <si>
+    <t>getString("/account/noSGBTransactionLast24Months") == "$1"</t>
+  </si>
+  <si>
+    <t>getString("/account/noMutualFundTransactionLast24Months") == "$1"</t>
+  </si>
+  <si>
+    <t>getString("/account/noInsuranceTransactionLast24Months") == "$1"</t>
+  </si>
+  <si>
+    <t>getString("/account/noNCDBondActivityLast24Months") == "$1"</t>
+  </si>
+  <si>
+    <t>getString("/account/noNSDLOrCDSLActivityLast24Months") == "$1"</t>
+  </si>
+  <si>
+    <t>getString("/account/noApprovedPayInPayOutLast24Months") == "$1"</t>
+  </si>
+  <si>
+    <t>getString("/account/noKRAInitialOrModificationLast24Months") == "$1"</t>
+  </si>
+  <si>
+    <t>getString("/account/noCKYCUploadOrModificationLast24Months") == "$1"</t>
+  </si>
+  <si>
+    <t>getString("/account/noApprovedCRFLast24Months") == "$1"</t>
+  </si>
+  <si>
+    <t>getString("/account/noExchangeTradingLast24Months") == "$1"</t>
+  </si>
+  <si>
+    <t>getString("/account/notTradedOnCurrentDate") == "$1"</t>
+  </si>
+  <si>
+    <t>getString("/account/activeNACH") == "$1"</t>
+  </si>
+  <si>
+    <t>getString("/account/activeSIP") == "$1"</t>
+  </si>
+  <si>
+    <t>getString("/account/valid3KYC/adhaar") == "$1"</t>
+  </si>
+  <si>
+    <t>getString("/account/valid3KYC/pan") == "$1"</t>
+  </si>
+  <si>
+    <t>getString("/account/valid3KYC/passport") == "$1"</t>
+  </si>
+  <si>
+    <t>getString("/account/compiledKRA") == "$1"</t>
+  </si>
+  <si>
+    <t>getString("/account/validCKYCNum") == "$1"</t>
+  </si>
+  <si>
+    <t>getString("/account/validPriBankAcc") == "$1"</t>
+  </si>
+  <si>
+    <t>getString("/account/validPriDP") == "$1"</t>
+  </si>
+  <si>
     <t>set("/account/output/permission", "$param");</t>
   </si>
   <si>
@@ -109,6 +178,75 @@
     <t>/account/noOFSActivityLast24Months</t>
   </si>
   <si>
+    <t>/account/noBuybackActivityLast24Months</t>
+  </si>
+  <si>
+    <t>/account/noOpenOfferActivityLast24Months</t>
+  </si>
+  <si>
+    <t>/account/noIPOSubscriptionLast24Months</t>
+  </si>
+  <si>
+    <t>/account/noSGBTransactionLast24Months</t>
+  </si>
+  <si>
+    <t>/account/noMutualFundTransactionLast24Months</t>
+  </si>
+  <si>
+    <t>/account/noInsuranceTransactionLast24Months</t>
+  </si>
+  <si>
+    <t>/account/noNCDBondActivityLast24Months</t>
+  </si>
+  <si>
+    <t>/account/noNSDLOrCDSLActivityLast24Months</t>
+  </si>
+  <si>
+    <t>/account/noApprovedPayInPayOutLast24Months</t>
+  </si>
+  <si>
+    <t>/account/noKRAInitialOrModificationLast24Months</t>
+  </si>
+  <si>
+    <t>/account/noCKYCUploadOrModificationLast24Months</t>
+  </si>
+  <si>
+    <t>/account/noApprovedCRFLast24Months</t>
+  </si>
+  <si>
+    <t>/account/noExchangeTradingLast24Months</t>
+  </si>
+  <si>
+    <t>/account/notTradedOnCurrentDate</t>
+  </si>
+  <si>
+    <t>/account/activeNACH</t>
+  </si>
+  <si>
+    <t>/account/activeSIP</t>
+  </si>
+  <si>
+    <t>/account/valid3KYC/adhaar</t>
+  </si>
+  <si>
+    <t>/account/valid3KYC/pan</t>
+  </si>
+  <si>
+    <t>/account/valid3KYC/passport</t>
+  </si>
+  <si>
+    <t>/account/compiledKRA</t>
+  </si>
+  <si>
+    <t>/account/validCKYCNum</t>
+  </si>
+  <si>
+    <t>/account/validPriBankAcc</t>
+  </si>
+  <si>
+    <t>/account/validPriDP</t>
+  </si>
+  <si>
     <t>Initial Status</t>
   </si>
   <si>
@@ -133,6 +271,75 @@
     <t>No OFS Activity</t>
   </si>
   <si>
+    <t>No Buy Back Activity</t>
+  </si>
+  <si>
+    <t>No Open Offer Activity</t>
+  </si>
+  <si>
+    <t>No IPO Subscription</t>
+  </si>
+  <si>
+    <t>No SGB Transaction</t>
+  </si>
+  <si>
+    <t>No Mutual Fund Transaction</t>
+  </si>
+  <si>
+    <t>No Insurance Transactions</t>
+  </si>
+  <si>
+    <t>No NCD Bond Activity</t>
+  </si>
+  <si>
+    <t>No NSDL/CDSL Activity</t>
+  </si>
+  <si>
+    <t>No Approved Pay in Pay out</t>
+  </si>
+  <si>
+    <t>No KRA Modification</t>
+  </si>
+  <si>
+    <t>No CKYC Activity</t>
+  </si>
+  <si>
+    <t>No Approved CRF</t>
+  </si>
+  <si>
+    <t>No Exchange Trading</t>
+  </si>
+  <si>
+    <t>Not Traded on Current Date</t>
+  </si>
+  <si>
+    <t>Active NACH</t>
+  </si>
+  <si>
+    <t>Active SIP</t>
+  </si>
+  <si>
+    <t>Valid Aadhaar</t>
+  </si>
+  <si>
+    <t>Valid PAN</t>
+  </si>
+  <si>
+    <t>Valid Passport</t>
+  </si>
+  <si>
+    <t>KRA Registered</t>
+  </si>
+  <si>
+    <t>Valid CKYC Number</t>
+  </si>
+  <si>
+    <t>Valid Primary Bank Account</t>
+  </si>
+  <si>
+    <t>Valid Primary DP</t>
+  </si>
+  <si>
     <t>Allowed</t>
   </si>
   <si>
@@ -193,6 +400,9 @@
     <t>sellingToFreeze</t>
   </si>
   <si>
+    <t>Y</t>
+  </si>
+  <si>
     <t>activeToSelllingOnly1</t>
   </si>
   <si>
@@ -200,9 +410,6 @@
   </si>
   <si>
     <t>SO</t>
-  </si>
-  <si>
-    <t>Y</t>
   </si>
   <si>
     <t>SELLING ONLY</t>
@@ -249,7 +456,7 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -324,6 +531,12 @@
         <bgColor auto="1"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="18"/>
+        <bgColor auto="1"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="5">
     <border>
@@ -391,7 +604,7 @@
       <alignment vertical="bottom"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
@@ -437,13 +650,16 @@
     <xf numFmtId="49" fontId="0" fillId="9" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="10" borderId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="0" fillId="10" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="10" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="0" fillId="11" borderId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="10" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="0" fillId="11" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="11" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
@@ -474,6 +690,7 @@
       <rgbColor rgb="fff19d64"/>
       <rgbColor rgb="ff93c175"/>
       <rgbColor rgb="ffaaaaaa"/>
+      <rgbColor rgb="fff19d64"/>
       <rgbColor rgb="ffadcdea"/>
     </indexedColors>
   </colors>
@@ -1509,13 +1726,21 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L19"/>
+  <dimension ref="A1:AI19"/>
   <sheetFormatPr defaultColWidth="16.3333" defaultRowHeight="15.4" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="2" width="28.6719" style="1" customWidth="1"/>
     <col min="3" max="10" width="45.6719" style="1" customWidth="1"/>
-    <col min="11" max="12" width="40.1719" style="1" customWidth="1"/>
-    <col min="13" max="16384" width="16.3516" style="1" customWidth="1"/>
+    <col min="11" max="11" width="49.9609" style="1" customWidth="1"/>
+    <col min="12" max="12" width="52.0781" style="1" customWidth="1"/>
+    <col min="13" max="14" width="49.2656" style="1" customWidth="1"/>
+    <col min="15" max="15" width="53.6719" style="1" customWidth="1"/>
+    <col min="16" max="16" width="51.8516" style="1" customWidth="1"/>
+    <col min="17" max="17" width="49.2656" style="1" customWidth="1"/>
+    <col min="18" max="18" width="51" style="1" customWidth="1"/>
+    <col min="19" max="33" width="49.2656" style="1" customWidth="1"/>
+    <col min="34" max="35" width="40.1719" style="1" customWidth="1"/>
+    <col min="36" max="16384" width="16.3516" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="21.05" customHeight="1">
@@ -1535,6 +1760,29 @@
       <c r="J1" s="4"/>
       <c r="K1" s="4"/>
       <c r="L1" s="4"/>
+      <c r="M1" s="4"/>
+      <c r="N1" s="4"/>
+      <c r="O1" s="4"/>
+      <c r="P1" s="4"/>
+      <c r="Q1" s="4"/>
+      <c r="R1" s="4"/>
+      <c r="S1" s="4"/>
+      <c r="T1" s="4"/>
+      <c r="U1" s="4"/>
+      <c r="V1" s="4"/>
+      <c r="W1" s="4"/>
+      <c r="X1" s="4"/>
+      <c r="Y1" s="4"/>
+      <c r="Z1" s="4"/>
+      <c r="AA1" s="4"/>
+      <c r="AB1" s="4"/>
+      <c r="AC1" s="4"/>
+      <c r="AD1" s="4"/>
+      <c r="AE1" s="4"/>
+      <c r="AF1" s="4"/>
+      <c r="AG1" s="4"/>
+      <c r="AH1" s="4"/>
+      <c r="AI1" s="4"/>
     </row>
     <row r="2" ht="21.05" customHeight="1">
       <c r="A2" s="2"/>
@@ -1553,6 +1801,29 @@
       <c r="J2" s="4"/>
       <c r="K2" s="4"/>
       <c r="L2" s="4"/>
+      <c r="M2" s="4"/>
+      <c r="N2" s="4"/>
+      <c r="O2" s="4"/>
+      <c r="P2" s="4"/>
+      <c r="Q2" s="4"/>
+      <c r="R2" s="4"/>
+      <c r="S2" s="4"/>
+      <c r="T2" s="4"/>
+      <c r="U2" s="4"/>
+      <c r="V2" s="4"/>
+      <c r="W2" s="4"/>
+      <c r="X2" s="4"/>
+      <c r="Y2" s="4"/>
+      <c r="Z2" s="4"/>
+      <c r="AA2" s="4"/>
+      <c r="AB2" s="4"/>
+      <c r="AC2" s="4"/>
+      <c r="AD2" s="4"/>
+      <c r="AE2" s="4"/>
+      <c r="AF2" s="4"/>
+      <c r="AG2" s="4"/>
+      <c r="AH2" s="4"/>
+      <c r="AI2" s="4"/>
     </row>
     <row r="3" ht="21.05" customHeight="1">
       <c r="A3" s="2"/>
@@ -1571,6 +1842,29 @@
       <c r="J3" s="4"/>
       <c r="K3" s="4"/>
       <c r="L3" s="4"/>
+      <c r="M3" s="4"/>
+      <c r="N3" s="4"/>
+      <c r="O3" s="4"/>
+      <c r="P3" s="4"/>
+      <c r="Q3" s="4"/>
+      <c r="R3" s="4"/>
+      <c r="S3" s="4"/>
+      <c r="T3" s="4"/>
+      <c r="U3" s="4"/>
+      <c r="V3" s="4"/>
+      <c r="W3" s="4"/>
+      <c r="X3" s="4"/>
+      <c r="Y3" s="4"/>
+      <c r="Z3" s="4"/>
+      <c r="AA3" s="4"/>
+      <c r="AB3" s="4"/>
+      <c r="AC3" s="4"/>
+      <c r="AD3" s="4"/>
+      <c r="AE3" s="4"/>
+      <c r="AF3" s="4"/>
+      <c r="AG3" s="4"/>
+      <c r="AH3" s="4"/>
+      <c r="AI3" s="4"/>
     </row>
     <row r="4" ht="21.05" customHeight="1">
       <c r="A4" s="6"/>
@@ -1587,6 +1881,29 @@
       <c r="J4" s="4"/>
       <c r="K4" s="4"/>
       <c r="L4" s="4"/>
+      <c r="M4" s="4"/>
+      <c r="N4" s="4"/>
+      <c r="O4" s="4"/>
+      <c r="P4" s="4"/>
+      <c r="Q4" s="4"/>
+      <c r="R4" s="4"/>
+      <c r="S4" s="4"/>
+      <c r="T4" s="4"/>
+      <c r="U4" s="4"/>
+      <c r="V4" s="4"/>
+      <c r="W4" s="4"/>
+      <c r="X4" s="4"/>
+      <c r="Y4" s="4"/>
+      <c r="Z4" s="4"/>
+      <c r="AA4" s="4"/>
+      <c r="AB4" s="4"/>
+      <c r="AC4" s="4"/>
+      <c r="AD4" s="4"/>
+      <c r="AE4" s="4"/>
+      <c r="AF4" s="4"/>
+      <c r="AG4" s="4"/>
+      <c r="AH4" s="4"/>
+      <c r="AI4" s="4"/>
     </row>
     <row r="5" ht="32.9" customHeight="1">
       <c r="A5" s="2"/>
@@ -1603,6 +1920,29 @@
       <c r="J5" s="4"/>
       <c r="K5" s="4"/>
       <c r="L5" s="4"/>
+      <c r="M5" s="4"/>
+      <c r="N5" s="4"/>
+      <c r="O5" s="4"/>
+      <c r="P5" s="4"/>
+      <c r="Q5" s="4"/>
+      <c r="R5" s="4"/>
+      <c r="S5" s="4"/>
+      <c r="T5" s="4"/>
+      <c r="U5" s="4"/>
+      <c r="V5" s="4"/>
+      <c r="W5" s="4"/>
+      <c r="X5" s="4"/>
+      <c r="Y5" s="4"/>
+      <c r="Z5" s="4"/>
+      <c r="AA5" s="4"/>
+      <c r="AB5" s="4"/>
+      <c r="AC5" s="4"/>
+      <c r="AD5" s="4"/>
+      <c r="AE5" s="4"/>
+      <c r="AF5" s="4"/>
+      <c r="AG5" s="4"/>
+      <c r="AH5" s="4"/>
+      <c r="AI5" s="4"/>
     </row>
     <row r="6" ht="21.15" customHeight="1">
       <c r="A6" t="s" s="8">
@@ -1635,10 +1975,79 @@
       <c r="J6" t="s" s="9">
         <v>10</v>
       </c>
-      <c r="K6" t="s" s="10">
+      <c r="K6" t="s" s="9">
+        <v>10</v>
+      </c>
+      <c r="L6" t="s" s="9">
+        <v>10</v>
+      </c>
+      <c r="M6" t="s" s="9">
+        <v>10</v>
+      </c>
+      <c r="N6" t="s" s="9">
+        <v>10</v>
+      </c>
+      <c r="O6" t="s" s="9">
+        <v>10</v>
+      </c>
+      <c r="P6" t="s" s="9">
+        <v>10</v>
+      </c>
+      <c r="Q6" t="s" s="9">
+        <v>10</v>
+      </c>
+      <c r="R6" t="s" s="9">
+        <v>10</v>
+      </c>
+      <c r="S6" t="s" s="9">
+        <v>10</v>
+      </c>
+      <c r="T6" t="s" s="9">
+        <v>10</v>
+      </c>
+      <c r="U6" t="s" s="9">
+        <v>10</v>
+      </c>
+      <c r="V6" t="s" s="9">
+        <v>10</v>
+      </c>
+      <c r="W6" t="s" s="9">
+        <v>10</v>
+      </c>
+      <c r="X6" t="s" s="9">
+        <v>10</v>
+      </c>
+      <c r="Y6" t="s" s="9">
+        <v>10</v>
+      </c>
+      <c r="Z6" t="s" s="9">
+        <v>10</v>
+      </c>
+      <c r="AA6" t="s" s="9">
+        <v>10</v>
+      </c>
+      <c r="AB6" t="s" s="9">
+        <v>10</v>
+      </c>
+      <c r="AC6" t="s" s="9">
+        <v>10</v>
+      </c>
+      <c r="AD6" t="s" s="9">
+        <v>10</v>
+      </c>
+      <c r="AE6" t="s" s="9">
+        <v>10</v>
+      </c>
+      <c r="AF6" t="s" s="9">
+        <v>10</v>
+      </c>
+      <c r="AG6" t="s" s="9">
+        <v>10</v>
+      </c>
+      <c r="AH6" t="s" s="10">
         <v>11</v>
       </c>
-      <c r="L6" t="s" s="10">
+      <c r="AI6" t="s" s="10">
         <v>11</v>
       </c>
     </row>
@@ -1655,10 +2064,33 @@
       <c r="H7" s="4"/>
       <c r="I7" s="4"/>
       <c r="J7" s="4"/>
-      <c r="K7" t="s" s="12">
+      <c r="K7" s="4"/>
+      <c r="L7" s="4"/>
+      <c r="M7" s="4"/>
+      <c r="N7" s="4"/>
+      <c r="O7" s="4"/>
+      <c r="P7" s="4"/>
+      <c r="Q7" s="4"/>
+      <c r="R7" s="4"/>
+      <c r="S7" s="4"/>
+      <c r="T7" s="4"/>
+      <c r="U7" s="4"/>
+      <c r="V7" s="4"/>
+      <c r="W7" s="4"/>
+      <c r="X7" s="4"/>
+      <c r="Y7" s="4"/>
+      <c r="Z7" s="4"/>
+      <c r="AA7" s="4"/>
+      <c r="AB7" s="4"/>
+      <c r="AC7" s="4"/>
+      <c r="AD7" s="4"/>
+      <c r="AE7" s="4"/>
+      <c r="AF7" s="4"/>
+      <c r="AG7" s="4"/>
+      <c r="AH7" t="s" s="12">
         <v>13</v>
       </c>
-      <c r="L7" t="s" s="13">
+      <c r="AI7" t="s" s="13">
         <v>13</v>
       </c>
     </row>
@@ -1689,403 +2121,1185 @@
       <c r="J8" t="s" s="11">
         <v>21</v>
       </c>
-      <c r="K8" t="s" s="14">
+      <c r="K8" t="s" s="11">
         <v>22</v>
       </c>
-      <c r="L8" t="s" s="14">
+      <c r="L8" t="s" s="11">
         <v>23</v>
       </c>
+      <c r="M8" t="s" s="11">
+        <v>24</v>
+      </c>
+      <c r="N8" t="s" s="11">
+        <v>25</v>
+      </c>
+      <c r="O8" t="s" s="11">
+        <v>26</v>
+      </c>
+      <c r="P8" t="s" s="11">
+        <v>27</v>
+      </c>
+      <c r="Q8" t="s" s="11">
+        <v>28</v>
+      </c>
+      <c r="R8" t="s" s="11">
+        <v>29</v>
+      </c>
+      <c r="S8" t="s" s="11">
+        <v>30</v>
+      </c>
+      <c r="T8" t="s" s="11">
+        <v>31</v>
+      </c>
+      <c r="U8" t="s" s="11">
+        <v>32</v>
+      </c>
+      <c r="V8" t="s" s="11">
+        <v>33</v>
+      </c>
+      <c r="W8" t="s" s="11">
+        <v>34</v>
+      </c>
+      <c r="X8" t="s" s="11">
+        <v>35</v>
+      </c>
+      <c r="Y8" t="s" s="11">
+        <v>36</v>
+      </c>
+      <c r="Z8" t="s" s="11">
+        <v>37</v>
+      </c>
+      <c r="AA8" t="s" s="11">
+        <v>38</v>
+      </c>
+      <c r="AB8" t="s" s="11">
+        <v>39</v>
+      </c>
+      <c r="AC8" t="s" s="11">
+        <v>40</v>
+      </c>
+      <c r="AD8" t="s" s="11">
+        <v>41</v>
+      </c>
+      <c r="AE8" t="s" s="11">
+        <v>42</v>
+      </c>
+      <c r="AF8" t="s" s="11">
+        <v>43</v>
+      </c>
+      <c r="AG8" t="s" s="11">
+        <v>44</v>
+      </c>
+      <c r="AH8" t="s" s="14">
+        <v>45</v>
+      </c>
+      <c r="AI8" t="s" s="14">
+        <v>46</v>
+      </c>
     </row>
-    <row r="9" ht="12.9" customHeight="1" hidden="1">
+    <row r="9" ht="12.9" customHeight="1">
       <c r="A9" s="6"/>
       <c r="B9" s="6"/>
-      <c r="C9" t="s" s="11">
-        <v>24</v>
-      </c>
-      <c r="D9" t="s" s="11">
-        <v>25</v>
-      </c>
-      <c r="E9" t="s" s="11">
-        <v>26</v>
-      </c>
-      <c r="F9" t="s" s="11">
-        <v>27</v>
-      </c>
-      <c r="G9" t="s" s="11">
-        <v>28</v>
-      </c>
-      <c r="H9" t="s" s="11">
-        <v>29</v>
-      </c>
-      <c r="I9" t="s" s="11">
-        <v>30</v>
-      </c>
-      <c r="J9" t="s" s="11">
-        <v>31</v>
-      </c>
-      <c r="K9" s="14"/>
-      <c r="L9" s="14"/>
+      <c r="C9" t="s" s="15">
+        <v>47</v>
+      </c>
+      <c r="D9" t="s" s="15">
+        <v>48</v>
+      </c>
+      <c r="E9" t="s" s="15">
+        <v>49</v>
+      </c>
+      <c r="F9" t="s" s="15">
+        <v>50</v>
+      </c>
+      <c r="G9" t="s" s="15">
+        <v>51</v>
+      </c>
+      <c r="H9" t="s" s="15">
+        <v>52</v>
+      </c>
+      <c r="I9" t="s" s="15">
+        <v>53</v>
+      </c>
+      <c r="J9" t="s" s="15">
+        <v>54</v>
+      </c>
+      <c r="K9" t="s" s="11">
+        <v>55</v>
+      </c>
+      <c r="L9" t="s" s="11">
+        <v>56</v>
+      </c>
+      <c r="M9" t="s" s="11">
+        <v>57</v>
+      </c>
+      <c r="N9" t="s" s="11">
+        <v>58</v>
+      </c>
+      <c r="O9" t="s" s="11">
+        <v>59</v>
+      </c>
+      <c r="P9" t="s" s="11">
+        <v>60</v>
+      </c>
+      <c r="Q9" t="s" s="11">
+        <v>61</v>
+      </c>
+      <c r="R9" t="s" s="11">
+        <v>62</v>
+      </c>
+      <c r="S9" t="s" s="11">
+        <v>63</v>
+      </c>
+      <c r="T9" t="s" s="11">
+        <v>64</v>
+      </c>
+      <c r="U9" t="s" s="11">
+        <v>65</v>
+      </c>
+      <c r="V9" t="s" s="11">
+        <v>66</v>
+      </c>
+      <c r="W9" t="s" s="11">
+        <v>67</v>
+      </c>
+      <c r="X9" t="s" s="11">
+        <v>68</v>
+      </c>
+      <c r="Y9" t="s" s="11">
+        <v>69</v>
+      </c>
+      <c r="Z9" t="s" s="11">
+        <v>70</v>
+      </c>
+      <c r="AA9" t="s" s="11">
+        <v>71</v>
+      </c>
+      <c r="AB9" t="s" s="11">
+        <v>72</v>
+      </c>
+      <c r="AC9" t="s" s="11">
+        <v>73</v>
+      </c>
+      <c r="AD9" t="s" s="11">
+        <v>74</v>
+      </c>
+      <c r="AE9" t="s" s="11">
+        <v>75</v>
+      </c>
+      <c r="AF9" t="s" s="11">
+        <v>76</v>
+      </c>
+      <c r="AG9" t="s" s="11">
+        <v>77</v>
+      </c>
+      <c r="AH9" s="14"/>
+      <c r="AI9" s="14"/>
     </row>
     <row r="10" ht="18.95" customHeight="1">
       <c r="A10" s="2"/>
       <c r="B10" s="2"/>
-      <c r="C10" t="s" s="15">
-        <v>32</v>
-      </c>
-      <c r="D10" t="s" s="16">
-        <v>33</v>
-      </c>
-      <c r="E10" t="s" s="16">
-        <v>34</v>
-      </c>
-      <c r="F10" t="s" s="16">
-        <v>35</v>
-      </c>
-      <c r="G10" t="s" s="16">
-        <v>36</v>
-      </c>
-      <c r="H10" t="s" s="16">
-        <v>37</v>
-      </c>
-      <c r="I10" t="s" s="16">
-        <v>38</v>
-      </c>
-      <c r="J10" t="s" s="16">
-        <v>39</v>
-      </c>
-      <c r="K10" t="s" s="16">
-        <v>40</v>
+      <c r="C10" t="s" s="16">
+        <v>78</v>
+      </c>
+      <c r="D10" t="s" s="17">
+        <v>79</v>
+      </c>
+      <c r="E10" t="s" s="17">
+        <v>80</v>
+      </c>
+      <c r="F10" t="s" s="17">
+        <v>81</v>
+      </c>
+      <c r="G10" t="s" s="17">
+        <v>82</v>
+      </c>
+      <c r="H10" t="s" s="17">
+        <v>83</v>
+      </c>
+      <c r="I10" t="s" s="17">
+        <v>84</v>
+      </c>
+      <c r="J10" t="s" s="17">
+        <v>85</v>
+      </c>
+      <c r="K10" t="s" s="17">
+        <v>86</v>
       </c>
       <c r="L10" t="s" s="17">
-        <v>41</v>
+        <v>87</v>
+      </c>
+      <c r="M10" t="s" s="17">
+        <v>88</v>
+      </c>
+      <c r="N10" t="s" s="17">
+        <v>89</v>
+      </c>
+      <c r="O10" t="s" s="17">
+        <v>90</v>
+      </c>
+      <c r="P10" t="s" s="17">
+        <v>91</v>
+      </c>
+      <c r="Q10" t="s" s="17">
+        <v>92</v>
+      </c>
+      <c r="R10" t="s" s="17">
+        <v>93</v>
+      </c>
+      <c r="S10" t="s" s="17">
+        <v>94</v>
+      </c>
+      <c r="T10" t="s" s="17">
+        <v>95</v>
+      </c>
+      <c r="U10" t="s" s="17">
+        <v>96</v>
+      </c>
+      <c r="V10" t="s" s="17">
+        <v>97</v>
+      </c>
+      <c r="W10" t="s" s="17">
+        <v>98</v>
+      </c>
+      <c r="X10" t="s" s="17">
+        <v>99</v>
+      </c>
+      <c r="Y10" t="s" s="17">
+        <v>100</v>
+      </c>
+      <c r="Z10" t="s" s="17">
+        <v>101</v>
+      </c>
+      <c r="AA10" t="s" s="17">
+        <v>102</v>
+      </c>
+      <c r="AB10" t="s" s="17">
+        <v>103</v>
+      </c>
+      <c r="AC10" t="s" s="17">
+        <v>104</v>
+      </c>
+      <c r="AD10" t="s" s="17">
+        <v>105</v>
+      </c>
+      <c r="AE10" t="s" s="17">
+        <v>106</v>
+      </c>
+      <c r="AF10" t="s" s="17">
+        <v>107</v>
+      </c>
+      <c r="AG10" t="s" s="17">
+        <v>108</v>
+      </c>
+      <c r="AH10" t="s" s="17">
+        <v>109</v>
+      </c>
+      <c r="AI10" t="s" s="18">
+        <v>110</v>
       </c>
     </row>
     <row r="11" ht="12.9" customHeight="1">
       <c r="A11" t="s" s="2">
-        <v>42</v>
+        <v>111</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>43</v>
-      </c>
-      <c r="C11" t="s" s="18">
-        <v>44</v>
-      </c>
-      <c r="D11" t="s" s="18">
-        <v>45</v>
-      </c>
-      <c r="E11" t="s" s="18">
-        <v>46</v>
-      </c>
-      <c r="F11" t="s" s="18">
-        <v>46</v>
-      </c>
-      <c r="G11" t="s" s="18">
-        <v>46</v>
-      </c>
-      <c r="H11" t="s" s="18">
-        <v>46</v>
-      </c>
-      <c r="I11" t="s" s="18">
-        <v>46</v>
-      </c>
-      <c r="J11" t="s" s="18">
-        <v>46</v>
-      </c>
-      <c r="K11" t="s" s="18">
-        <v>47</v>
-      </c>
-      <c r="L11" t="s" s="18">
-        <v>48</v>
+        <v>112</v>
+      </c>
+      <c r="C11" t="s" s="19">
+        <v>113</v>
+      </c>
+      <c r="D11" t="s" s="19">
+        <v>114</v>
+      </c>
+      <c r="E11" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="F11" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="G11" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="H11" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="I11" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="J11" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="K11" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="L11" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="M11" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="N11" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="O11" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="P11" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="Q11" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="R11" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="S11" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="T11" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="U11" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="V11" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="W11" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="X11" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="Y11" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="Z11" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="AA11" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="AB11" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="AC11" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="AD11" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="AE11" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="AF11" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="AG11" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="AH11" t="s" s="19">
+        <v>116</v>
+      </c>
+      <c r="AI11" t="s" s="19">
+        <v>117</v>
       </c>
     </row>
     <row r="12" ht="12.9" customHeight="1">
       <c r="A12" t="s" s="2">
-        <v>49</v>
+        <v>118</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>43</v>
-      </c>
-      <c r="C12" t="s" s="18">
-        <v>44</v>
-      </c>
-      <c r="D12" t="s" s="18">
-        <v>45</v>
-      </c>
-      <c r="E12" t="s" s="18">
-        <v>46</v>
-      </c>
-      <c r="F12" t="s" s="18">
-        <v>46</v>
-      </c>
-      <c r="G12" t="s" s="18">
-        <v>46</v>
-      </c>
-      <c r="H12" t="s" s="18">
-        <v>46</v>
-      </c>
-      <c r="I12" t="s" s="18">
-        <v>46</v>
-      </c>
-      <c r="J12" t="s" s="18">
-        <v>46</v>
-      </c>
-      <c r="K12" t="s" s="18">
-        <v>47</v>
-      </c>
-      <c r="L12" t="s" s="18">
-        <v>48</v>
+        <v>112</v>
+      </c>
+      <c r="C12" t="s" s="19">
+        <v>113</v>
+      </c>
+      <c r="D12" t="s" s="19">
+        <v>114</v>
+      </c>
+      <c r="E12" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="F12" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="G12" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="H12" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="I12" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="J12" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="K12" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="L12" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="M12" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="N12" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="O12" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="P12" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="Q12" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="R12" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="S12" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="T12" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="U12" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="V12" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="W12" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="X12" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="Y12" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="Z12" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="AA12" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="AB12" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="AC12" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="AD12" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="AE12" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="AF12" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="AG12" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="AH12" t="s" s="19">
+        <v>116</v>
+      </c>
+      <c r="AI12" t="s" s="19">
+        <v>117</v>
       </c>
     </row>
     <row r="13" ht="12.9" customHeight="1">
       <c r="A13" t="s" s="2">
-        <v>50</v>
+        <v>119</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>51</v>
-      </c>
-      <c r="C13" t="s" s="18">
-        <v>44</v>
-      </c>
-      <c r="D13" t="s" s="18">
-        <v>52</v>
-      </c>
-      <c r="E13" t="s" s="18">
-        <v>46</v>
-      </c>
-      <c r="F13" t="s" s="18">
-        <v>46</v>
-      </c>
-      <c r="G13" t="s" s="18">
-        <v>46</v>
-      </c>
-      <c r="H13" t="s" s="18">
-        <v>46</v>
-      </c>
-      <c r="I13" t="s" s="18">
-        <v>46</v>
-      </c>
-      <c r="J13" t="s" s="18">
-        <v>46</v>
-      </c>
-      <c r="K13" t="s" s="18">
-        <v>47</v>
-      </c>
-      <c r="L13" t="s" s="18">
-        <v>53</v>
+        <v>120</v>
+      </c>
+      <c r="C13" t="s" s="19">
+        <v>113</v>
+      </c>
+      <c r="D13" t="s" s="19">
+        <v>121</v>
+      </c>
+      <c r="E13" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="F13" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="G13" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="H13" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="I13" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="J13" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="K13" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="L13" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="M13" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="N13" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="O13" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="P13" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="Q13" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="R13" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="S13" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="T13" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="U13" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="V13" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="W13" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="X13" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="Y13" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="Z13" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="AA13" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="AB13" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="AC13" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="AD13" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="AE13" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="AF13" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="AG13" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="AH13" t="s" s="19">
+        <v>116</v>
+      </c>
+      <c r="AI13" t="s" s="19">
+        <v>122</v>
       </c>
     </row>
     <row r="14" ht="12.9" customHeight="1">
       <c r="A14" t="s" s="2">
-        <v>54</v>
+        <v>123</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>55</v>
-      </c>
-      <c r="C14" t="s" s="18">
-        <v>44</v>
-      </c>
-      <c r="D14" t="s" s="18">
-        <v>56</v>
-      </c>
-      <c r="E14" t="s" s="18">
-        <v>46</v>
-      </c>
-      <c r="F14" t="s" s="18">
-        <v>46</v>
-      </c>
-      <c r="G14" t="s" s="18">
-        <v>46</v>
-      </c>
-      <c r="H14" t="s" s="18">
-        <v>46</v>
-      </c>
-      <c r="I14" t="s" s="18">
-        <v>46</v>
-      </c>
-      <c r="J14" t="s" s="18">
-        <v>46</v>
-      </c>
-      <c r="K14" t="s" s="18">
-        <v>47</v>
-      </c>
-      <c r="L14" t="s" s="18">
-        <v>57</v>
+        <v>124</v>
+      </c>
+      <c r="C14" t="s" s="19">
+        <v>113</v>
+      </c>
+      <c r="D14" t="s" s="19">
+        <v>125</v>
+      </c>
+      <c r="E14" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="F14" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="G14" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="H14" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="I14" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="J14" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="K14" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="L14" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="M14" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="N14" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="O14" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="P14" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="Q14" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="R14" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="S14" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="T14" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="U14" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="V14" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="W14" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="X14" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="Y14" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="Z14" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="AA14" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="AB14" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="AC14" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="AD14" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="AE14" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="AF14" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="AG14" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="AH14" t="s" s="19">
+        <v>116</v>
+      </c>
+      <c r="AI14" t="s" s="19">
+        <v>126</v>
       </c>
     </row>
     <row r="15" ht="12.9" customHeight="1">
       <c r="A15" t="s" s="2">
-        <v>58</v>
+        <v>127</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>59</v>
-      </c>
-      <c r="C15" t="s" s="18">
-        <v>52</v>
-      </c>
-      <c r="D15" t="s" s="18">
-        <v>45</v>
-      </c>
-      <c r="E15" t="s" s="18">
-        <v>46</v>
-      </c>
-      <c r="F15" t="s" s="18">
-        <v>46</v>
-      </c>
-      <c r="G15" t="s" s="18">
-        <v>46</v>
-      </c>
-      <c r="H15" t="s" s="18">
-        <v>46</v>
-      </c>
-      <c r="I15" t="s" s="18">
-        <v>46</v>
-      </c>
-      <c r="J15" t="s" s="18">
-        <v>46</v>
-      </c>
-      <c r="K15" t="s" s="18">
-        <v>47</v>
-      </c>
-      <c r="L15" t="s" s="18">
-        <v>48</v>
+        <v>128</v>
+      </c>
+      <c r="C15" t="s" s="19">
+        <v>121</v>
+      </c>
+      <c r="D15" t="s" s="19">
+        <v>114</v>
+      </c>
+      <c r="E15" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="F15" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="G15" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="H15" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="I15" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="J15" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="K15" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="L15" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="M15" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="N15" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="O15" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="P15" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="Q15" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="R15" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="S15" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="T15" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="U15" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="V15" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="W15" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="X15" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="Y15" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="Z15" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="AA15" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="AB15" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="AC15" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="AD15" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="AE15" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="AF15" t="s" s="19">
+        <v>129</v>
+      </c>
+      <c r="AG15" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="AH15" t="s" s="19">
+        <v>116</v>
+      </c>
+      <c r="AI15" t="s" s="19">
+        <v>117</v>
       </c>
     </row>
     <row r="16" ht="12.9" customHeight="1">
       <c r="A16" t="s" s="2">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>61</v>
-      </c>
-      <c r="C16" t="s" s="18">
-        <v>44</v>
-      </c>
-      <c r="D16" t="s" s="18">
-        <v>62</v>
-      </c>
-      <c r="E16" t="s" s="18">
-        <v>63</v>
-      </c>
-      <c r="F16" t="s" s="18">
-        <v>46</v>
-      </c>
-      <c r="G16" t="s" s="18">
-        <v>63</v>
-      </c>
-      <c r="H16" t="s" s="18">
-        <v>46</v>
-      </c>
-      <c r="I16" t="s" s="18">
-        <v>46</v>
-      </c>
-      <c r="J16" t="s" s="18">
-        <v>63</v>
-      </c>
-      <c r="K16" t="s" s="18">
-        <v>47</v>
-      </c>
-      <c r="L16" t="s" s="18">
-        <v>64</v>
+        <v>131</v>
+      </c>
+      <c r="C16" t="s" s="19">
+        <v>113</v>
+      </c>
+      <c r="D16" t="s" s="19">
+        <v>132</v>
+      </c>
+      <c r="E16" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="F16" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="G16" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="H16" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="I16" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="J16" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="K16" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="L16" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="M16" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="N16" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="O16" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="P16" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="Q16" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="R16" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="S16" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="T16" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="U16" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="V16" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="W16" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="X16" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="Y16" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="Z16" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="AA16" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="AB16" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="AC16" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="AD16" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="AE16" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="AF16" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="AG16" t="s" s="19">
+        <v>129</v>
+      </c>
+      <c r="AH16" t="s" s="19">
+        <v>116</v>
+      </c>
+      <c r="AI16" t="s" s="19">
+        <v>133</v>
       </c>
     </row>
     <row r="17" ht="12.9" customHeight="1">
       <c r="A17" t="s" s="2">
-        <v>65</v>
+        <v>134</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>61</v>
-      </c>
-      <c r="C17" t="s" s="18">
-        <v>44</v>
-      </c>
-      <c r="D17" t="s" s="18">
-        <v>62</v>
-      </c>
-      <c r="E17" t="s" s="18">
-        <v>46</v>
-      </c>
-      <c r="F17" t="s" s="18">
-        <v>46</v>
-      </c>
-      <c r="G17" t="s" s="18">
-        <v>46</v>
-      </c>
-      <c r="H17" t="s" s="18">
-        <v>63</v>
-      </c>
-      <c r="I17" t="s" s="18">
-        <v>46</v>
-      </c>
-      <c r="J17" t="s" s="18">
-        <v>46</v>
-      </c>
-      <c r="K17" t="s" s="18">
-        <v>47</v>
-      </c>
-      <c r="L17" t="s" s="18">
-        <v>64</v>
+        <v>131</v>
+      </c>
+      <c r="C17" t="s" s="19">
+        <v>113</v>
+      </c>
+      <c r="D17" t="s" s="19">
+        <v>132</v>
+      </c>
+      <c r="E17" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="F17" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="G17" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="H17" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="I17" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="J17" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="K17" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="L17" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="M17" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="N17" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="O17" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="P17" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="Q17" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="R17" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="S17" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="T17" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="U17" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="V17" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="W17" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="X17" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="Y17" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="Z17" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="AA17" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="AB17" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="AC17" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="AD17" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="AE17" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="AF17" t="s" s="19">
+        <v>129</v>
+      </c>
+      <c r="AG17" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="AH17" t="s" s="19">
+        <v>116</v>
+      </c>
+      <c r="AI17" t="s" s="19">
+        <v>133</v>
       </c>
     </row>
     <row r="18" ht="12.9" customHeight="1">
       <c r="A18" t="s" s="2">
-        <v>66</v>
+        <v>135</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>61</v>
-      </c>
-      <c r="C18" t="s" s="18">
-        <v>44</v>
-      </c>
-      <c r="D18" t="s" s="18">
-        <v>62</v>
-      </c>
-      <c r="E18" t="s" s="18">
-        <v>46</v>
-      </c>
-      <c r="F18" t="s" s="18">
-        <v>46</v>
-      </c>
-      <c r="G18" t="s" s="18">
-        <v>46</v>
-      </c>
-      <c r="H18" t="s" s="18">
-        <v>46</v>
-      </c>
-      <c r="I18" t="s" s="18">
-        <v>46</v>
-      </c>
-      <c r="J18" t="s" s="18">
-        <v>46</v>
-      </c>
-      <c r="K18" t="s" s="18">
-        <v>47</v>
-      </c>
-      <c r="L18" t="s" s="18">
-        <v>64</v>
+        <v>131</v>
+      </c>
+      <c r="C18" t="s" s="19">
+        <v>113</v>
+      </c>
+      <c r="D18" t="s" s="19">
+        <v>132</v>
+      </c>
+      <c r="E18" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="F18" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="G18" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="H18" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="I18" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="J18" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="K18" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="L18" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="M18" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="N18" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="O18" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="P18" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="Q18" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="R18" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="S18" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="T18" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="U18" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="V18" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="W18" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="X18" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="Y18" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="Z18" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="AA18" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="AB18" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="AC18" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="AD18" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="AE18" t="s" s="19">
+        <v>129</v>
+      </c>
+      <c r="AF18" t="s" s="19">
+        <v>115</v>
+      </c>
+      <c r="AG18" t="s" s="19">
+        <v>129</v>
+      </c>
+      <c r="AH18" t="s" s="19">
+        <v>116</v>
+      </c>
+      <c r="AI18" t="s" s="19">
+        <v>133</v>
       </c>
     </row>
     <row r="19" ht="12.9" customHeight="1">
       <c r="A19" s="2"/>
       <c r="B19" s="2"/>
-      <c r="C19" s="18"/>
-      <c r="D19" s="18"/>
-      <c r="E19" s="18"/>
-      <c r="F19" s="18"/>
-      <c r="G19" s="18"/>
-      <c r="H19" s="18"/>
-      <c r="I19" s="18"/>
-      <c r="J19" s="18"/>
-      <c r="K19" s="18"/>
-      <c r="L19" s="18"/>
+      <c r="C19" s="19"/>
+      <c r="D19" s="19"/>
+      <c r="E19" s="19"/>
+      <c r="F19" s="19"/>
+      <c r="G19" s="19"/>
+      <c r="H19" s="19"/>
+      <c r="I19" s="19"/>
+      <c r="J19" s="19"/>
+      <c r="K19" s="19"/>
+      <c r="L19" s="19"/>
+      <c r="M19" s="19"/>
+      <c r="N19" s="19"/>
+      <c r="O19" s="19"/>
+      <c r="P19" s="19"/>
+      <c r="Q19" s="19"/>
+      <c r="R19" s="19"/>
+      <c r="S19" s="19"/>
+      <c r="T19" s="19"/>
+      <c r="U19" s="19"/>
+      <c r="V19" s="19"/>
+      <c r="W19" s="19"/>
+      <c r="X19" s="19"/>
+      <c r="Y19" s="19"/>
+      <c r="Z19" s="19"/>
+      <c r="AA19" s="19"/>
+      <c r="AB19" s="19"/>
+      <c r="AC19" s="19"/>
+      <c r="AD19" s="19"/>
+      <c r="AE19" s="19"/>
+      <c r="AF19" s="19"/>
+      <c r="AG19" s="19"/>
+      <c r="AH19" s="19"/>
+      <c r="AI19" s="19"/>
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="C7:J7"/>
-    <mergeCell ref="D1:L1"/>
-    <mergeCell ref="D2:L2"/>
-    <mergeCell ref="D3:L3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="D4:L4"/>
+    <mergeCell ref="C7:AG7"/>
+    <mergeCell ref="D1:AI1"/>
+    <mergeCell ref="D2:AI2"/>
+    <mergeCell ref="D3:AI3"/>
+    <mergeCell ref="C5:AI5"/>
+    <mergeCell ref="D4:AI4"/>
   </mergeCells>
   <pageMargins left="1" right="1" top="1" bottom="1" header="0.25" footer="0.25"/>
   <pageSetup firstPageNumber="1" fitToHeight="1" fitToWidth="1" scale="100" useFirstPageNumber="0" orientation="portrait" pageOrder="downThenOver"/>
